--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citations'!$A$1:$K$8</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -46,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +58,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="006B7280"/>
+        <color rgb="FF6B7280"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -77,7 +80,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -440,8 +443,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
@@ -456,7 +459,7 @@
     <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -513,7 +516,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>BIL2012</t>
@@ -568,7 +571,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>DUR2019</t>
@@ -623,7 +626,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GRI2020</t>
@@ -678,7 +681,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>WAS2004</t>
@@ -729,7 +732,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SHA2014</t>
@@ -780,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BIS2006</t>
@@ -831,7 +834,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>KOL2009</t>
@@ -956,7 +959,6 @@
       <c r="D10" t="n">
         <v>2016</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>MIT Press</t>
@@ -1007,13 +1009,11 @@
       <c r="D11" t="n">
         <v>2021</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>IEEE TPAMI 43(11)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>https://doi.org/10.1109/TPAMI.2020.2992934</t>
@@ -1032,6 +1032,76 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>Survey of normalizing flows — change of variables as engine of generative modeling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HAS2009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trevor Hastie, Robert Tibshirani &amp; Jerome Friedman</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The Elements of Statistical Learning</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>978-0-387-84857-0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://hastie.su.domains/ElemStatLearn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BLE2017</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>David M. Blei, Alp Kucukelbir &amp; Jon D. McAuliffe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Variational Inference: A Review for Statisticians</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JASA 112(518):859-877</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.2017.1285773</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>conditional-probability, random-variables</t>
+          <t>conditional-probability, random-variables, large-deviations</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables</t>
+          <t>random-variables, large-deviations</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1102,6 +1102,214 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/01621459.2017.1285773</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BLM2013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Stéphane Boucheron, Gábor Lugosi &amp; Pascal Massart</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Concentration Inequalities: A Nonasymptotic Theory of Independence</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Oxford University Press</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>978-0-19-953525-5</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://global.oup.com/academic/product/concentration-inequalities-9780199535255</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>large-deviations</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Definitive reference for concentration inequalities; sub-Gaussian, bounded-differences, entropy method</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>VER2018</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Roman Vershynin</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>High-Dimensional Probability: An Introduction with Applications to Data Science</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>978-1-108-41519-4</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.math.uci.edu/~rvershyn/papers/HDP-book/HDP-book.html</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>large-deviations</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Modern accessible treatment of sub-Gaussian/sub-exponential variables via Orlicz norms</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>WAI2019</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Martin J. Wainwright</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>High-Dimensional Statistics: A Non-Asymptotic Viewpoint</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>978-1-108-49802-9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cambridge.org/highereducation/books/high-dimensional-statistics/8A91ECEEC38F46DAB53E9FF8757D7A4E</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>large-deviations</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Concentration inequalities with applications to PAC learning and Rademacher complexity</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DZ2010</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Amir Dembo &amp; Ofer Zeitouni</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Large Deviations Techniques and Applications</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>978-3-642-03310-0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-3-642-03311-7</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>large-deviations</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Standard graduate reference for large deviations theory; Cramér, Sanov, Varadhan</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>conditional-probability, random-variables, large-deviations</t>
+          <t>conditional-probability, random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations</t>
+          <t>random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1074,6 +1074,21 @@
           <t>https://hastie.su.domains/ElemStatLearn/</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>point-estimation</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ch 7.3: bias-variance decomposition for prediction error — the ML version of the MSE decomposition</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1310,6 +1325,161 @@
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Standard graduate reference for large deviations theory; Cramér, Sanov, Varadhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LEH1998</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Erich L. Lehmann &amp; George Casella</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Theory of Point Estimation</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>978-0-387-98502-2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/b98854</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>point-estimation</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Definitive graduate-level reference on point estimation. Ch 1-2 cover unbiasedness, MSE, and the CRLB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BIC2015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Peter J. Bickel &amp; Kjell A. Doksum</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mathematical Statistics: Basic Ideas and Selected Topics</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CRC Press</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>978-1-498-72380-0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.routledge.com/Mathematical-Statistics-Basic-Ideas-and-Selected-Topics-Volume-I/Bickel-Doksum/p/book/9781498723800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>point-estimation</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ch 3: Fisher information, score function, CRLB with careful regularity-condition exposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STE1956</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Charles Stein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Inadmissibility of the Usual Estimator for the Mean of a Multivariate Normal Distribution</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1956</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Proceedings of the Third Berkeley Symposium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/euclid.bsmsp/1200501656</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>point-estimation</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Vol 1, pp 197-206. Original proof that the sample mean is inadmissible in dimension d &gt;= 3. Foundation of shrinkage estimation.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>conditional-probability, random-variables, large-deviations, point-estimation</t>
+          <t>conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation</t>
+          <t>point-estimation, maximum-likelihood</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>point-estimation</t>
+          <t>point-estimation, maximum-likelihood</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1480,6 +1480,116 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>Vol 1, pp 197-206. Original proof that the sample mean is inadmissible in dimension d &gt;= 3. Foundation of shrinkage estimation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VDV1998</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A. W. van der Vaart</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Asymptotic Statistics</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>978-0-521-78450-4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.cambridge.org/core/books/asymptotic-statistics/A3C7DAD3F7E66A1FA60E9C8FE132EE1D</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>maximum-likelihood</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Chapter 5 (M-Estimators and Maximum Likelihood) gives the modern treatment of MLE asymptotics. Theorem 5.39 is the asymptotic-normality result followed in Topic 14 §14.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NOC2006</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jorge Nocedal &amp; Stephen J. Wright</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Numerical Optimization</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>978-0-387-30303-1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-0-387-40065-5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>maximum-likelihood</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Chapter 2 covers Newton's method and quadratic convergence theory; Chapter 11 treats Fisher scoring and related maximum-likelihood iterations. Used in Topic 14 §14.7.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood</t>
+          <t>conditional-probability, random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood</t>
+          <t>random-variables, large-deviations, point-estimation</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood</t>
+          <t>point-estimation</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood</t>
+          <t>point-estimation</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1480,116 +1480,6 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>Vol 1, pp 197-206. Original proof that the sample mean is inadmissible in dimension d &gt;= 3. Foundation of shrinkage estimation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VDV1998</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>A. W. van der Vaart</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Asymptotic Statistics</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1998</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Cambridge University Press</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>978-0-521-78450-4</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.cambridge.org/core/books/asymptotic-statistics/A3C7DAD3F7E66A1FA60E9C8FE132EE1D</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Book</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>maximum-likelihood</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Chapter 5 (M-Estimators and Maximum Likelihood) gives the modern treatment of MLE asymptotics. Theorem 5.39 is the asymptotic-normality result followed in Topic 14 §14.5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NOC2006</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Jorge Nocedal &amp; Stephen J. Wright</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Numerical Optimization</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2006</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Springer</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>978-0-387-30303-1</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/book/10.1007/978-0-387-40065-5</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Book</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>maximum-likelihood</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Chapter 2 covers Newton's method and quadratic convergence theory; Chapter 11 treats Fisher scoring and related maximum-likelihood iterations. Used in Topic 14 §14.7.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood</t>
+          <t>point-estimation, maximum-likelihood, method-of-moments</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maximum-likelihood</t>
+          <t>maximum-likelihood, method-of-moments</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1590,6 +1590,202 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>Chapter 2 covers Newton's method and quadratic convergence theory; Chapter 11 treats Fisher scoring and related maximum-likelihood iterations. Used in Topic 14 §14.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HUB1964</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Peter J. Huber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Robust Estimation of a Location Parameter</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1964</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 35(1):73-101</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/euclid.aoms/1177703732</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>method-of-moments</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>The founding paper of M-estimation. Huber ψ-function, minimax property, and the sandwich variance. Primary reference for Topic 15 §15.9-§15.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HAM1986</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Frank R. Hampel, Elvezio M. Ronchetti, Peter J. Rousseeuw &amp; Werner A. Stahel</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Robust Statistics: The Approach Based on Influence Functions</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1986</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>978-0-471-82921-8</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.wiley.com/en-us/Robust+Statistics%3A+The+Approach+Based+on+Influence+Functions-p-9780471828921</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>method-of-moments</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ch 2 develops the influence function perspective on M-estimators. Tukey biweight, breakdown point, redescending ψ-functions — foundation for Topic 15 §15.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ROU1987</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Peter J. Rousseeuw &amp; Annick M. Leroy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Robust Regression and Outlier Detection</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>978-0-471-85233-9</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/0471725382</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>method-of-moments</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Canonical reference for Huber and Tukey M-estimators in regression. Ch 1 defines the breakdown point used in Topic 15 §15.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HAN1982</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lars Peter Hansen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Large Sample Properties of Generalized Method of Moments Estimators</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1982</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Econometrica 50(4):1029-1054</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/1912775</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>method-of-moments</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>The GMM paper. Cited in Topic 15 §15.12 as the forward link to the generalized method of moments. DOI 10.2307/1912775.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood, method-of-moments</t>
+          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1612,13 +1612,11 @@
       <c r="D23" t="n">
         <v>1964</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Annals of Mathematical Statistics 35(1):73-101</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>https://projecteuclid.org/euclid.aoms/1177703732</t>
@@ -1659,7 +1657,6 @@
       <c r="D24" t="n">
         <v>1986</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Wiley</t>
@@ -1710,7 +1707,6 @@
       <c r="D25" t="n">
         <v>1987</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Wiley</t>
@@ -1761,13 +1757,11 @@
       <c r="D26" t="n">
         <v>1982</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Econometrica 50(4):1029-1054</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>https://www.jstor.org/stable/1912775</t>
@@ -1786,6 +1780,446 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>The GMM paper. Cited in Topic 15 §15.12 as the forward link to the generalized method of moments. DOI 10.2307/1912775.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FIS1922</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ronald A. Fisher</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>On the Mathematical Foundations of Theoretical Statistics</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1922</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Philosophical Transactions of the Royal Society A</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://royalsocietypublishing.org/doi/10.1098/rsta.1922.0009</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Introduction of sufficient statistics (§7 of paper); cited in §16.1 as the historical origin of the concept</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HAL1949</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Paul R. Halmos &amp; Leonard J. Savage</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Application of the Radon-Nikodym Theorem to the Theory of Sufficient Statistics</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1949</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/euclid.aoms/1177730032</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Measure-theoretic formalization of the factorization theorem; cited §16.1 Remark 1 and §16.3 for rigor background</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RAO1945</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C. Radhakrishna Rao</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Information and the Accuracy Attainable in the Estimation of Statistical Parameters</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bulletin of the Calcutta Mathematical Society</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Rao’s original conditioning-inequality argument (pre-Blackwell); cited jointly as Rao (1945) / Blackwell (1947) in §16.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BLA1947</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>David Blackwell</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Conditional Expectation and Unbiased Sequential Estimation</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1947</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/euclid.aoms/1177730497</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Blackwell’s independent derivation / extension of Rao’s theorem; "Rao-Blackwell theorem" combines both (§16.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LEH1950</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Erich L. Lehmann &amp; Henry Scheffé</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Completeness, Similar Regions, and Unbiased Estimation — Part I</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sankhyā</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/25048038</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Foundational paper on completeness and UMVUE; cited §16.6 and §16.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BAS1955</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Debabrata Basu</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>On Statistics Independent of a Complete Sufficient Statistic</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1955</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sankhyā</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/25048259</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Basu’s theorem in its original form; the §16.9 proof follows Basu’s own argument</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DAR1935</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Georges Darmois</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sur les lois de probabilité à estimation exhaustive</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1935</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Comptes rendus de l’Académie des Sciences</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Darmois’ original scalar PKD characterization; §16.10 proof follows his cross-differentiation argument</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>KOO1936</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bernard O. Koopman</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>On Distributions Admitting a Sufficient Statistic</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1936</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Transactions of the American Mathematical Society</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/1989758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Koopman’s independent derivation of the characterization theorem; joint attribution with Darmois and Pitman (§16.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PIT1936</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>E. J. G. Pitman</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sufficient Statistics and Intrinsic Accuracy</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1936</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mathematical Proceedings of the Cambridge Philosophical Society</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/S0305004100019307</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Pitman’s independent derivation, giving the theorem the third name it bears (§16.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BRO1986</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lawrence D. Brown</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fundamentals of Statistical Exponential Families</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>IMS Lecture Notes Monograph Series, Vol. 9</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/euclid.lnms/1215466757</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>sufficient-statistics</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Definitive treatment of exponential families with the full $k$-parameter Pitman-Koopman-Darmois theorem; cited §16.10 Remark 11</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>sufficient-statistics</t>
+          <t>sufficient-statistics, hypothesis-testing</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2220,6 +2220,466 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>Definitive treatment of exponential families with the full $k$-parameter Pitman-Koopman-Darmois theorem; cited §16.10 Remark 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LEH2005</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Erich L. Lehmann &amp; Joseph P. Romano</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Testing Statistical Hypotheses</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>978-0-387-98864-1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/0-387-27605-X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ch 3 (UMP tests), Ch 12 (large-sample theory). Definitive modern treatment — notation and structure of §17 follow Lehmann-Romano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NEY1933</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jerzy Neyman &amp; Egon S. Pearson</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>On the Problem of the Most Efficient Tests of Statistical Hypotheses</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1933</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Philosophical Transactions of the Royal Society A</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1098/rsta.1933.0009</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Foundational NP paper: Type I/II errors, size, power, NP lemma. Cited in §17.1 (framing) and §17.4; lemma proved in Topic 18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STU1908</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>'Student' (William Sealy Gosset)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>The Probable Error of a Mean</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1908</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Biometrika</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2331554</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Gosset's derivation of the t distribution. Cited in §17.7's historical note; full rigorous derivation via Basu in §17.7 Thm 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PEA1900</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Karl Pearson</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>On the Criterion that a Given System of Deviations from the Probable is Such that It Can Be Reasonably Supposed to Have Arisen from Random Sampling</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Philosophical Magazine (5th series)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/14786440009463897</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Pearson's introduction of the chi-squared goodness-of-fit test. Cited in §17.8 history; modern derivation via continuous mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WAL1943</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Abraham Wald</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tests of Statistical Hypotheses Concerning Several Parameters When the Number of Observations is Large</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1943</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Transactions of the American Mathematical Society</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1090/S0002-9947-1943-0012401-3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Wald's definition of the Wald test and its asymptotic chi-squared distribution. Cited in §17.9 Def 13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RAO1948</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C. Radhakrishna Rao</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Large Sample Tests of Statistical Hypotheses Concerning Several Parameters with Applications to Problems of Estimation</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1948</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mathematical Proceedings of the Cambridge Philosophical Society</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/S0305004100023987</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Rao's definition of the score test. Cited in §17.9 Def 14. Distinct from RAO1945 (Rao-Blackwell, Topic 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WIL1938</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Samuel S. Wilks</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The Large-Sample Distribution of the Likelihood Ratio for Testing Composite Hypotheses</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1938</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/euclid.aoms/1177732360</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Wilks' theorem: -2 log Lambda → chi^2_k under regularity. Stated in §17.9 Thm 7; full proof deferred to Topic 18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WAS2016</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ronald L. Wasserstein &amp; Nicole A. Lazar</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>The ASA's Statement on p-Values: Context, Process, and Purpose</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The American Statistician</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/00031305.2016.1154108</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ASA's consensus on p-value misuse. Cited in §17.5 Remark 6. Full multiple-testing treatment in Topic 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IOA2005</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>John P. A. Ioannidis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Why Most Published Research Findings Are False</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PLoS Medicine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pmed.0020124</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Prior-probability argument for the replication crisis. Cited in §17.5 Remark 6 as the canonical 'p-values are not posterior probabilities' warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GEL2013</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Andrew Gelman &amp; Eric Loken</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The Garden of Forking Paths: Why Multiple Comparisons Can Be a Problem, Even When There is No 'Fishing Expedition' or 'p-Hacking'</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Department of Statistics, Columbia University</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://www.stat.columbia.edu/~gelman/research/unpublished/p_hacking.pdf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hypothesis-testing</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Researcher-degrees-of-freedom inflate Type I error even in good-faith analyses. Cited in §17.5 Remark 6 as the conceptual preview of Topic 20.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>sufficient-statistics</t>
+          <t>sufficient-statistics, confidence-intervals-and-duality</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>hypothesis-testing</t>
+          <t>hypothesis-testing, confidence-intervals-and-duality</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>hypothesis-testing</t>
+          <t>hypothesis-testing, confidence-intervals-and-duality</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>hypothesis-testing</t>
+          <t>hypothesis-testing, confidence-intervals-and-duality</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2680,6 +2680,288 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>Researcher-degrees-of-freedom inflate Type I error even in good-faith analyses. Cited in §17.5 Remark 6 as the conceptual preview of Topic 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WIL1927</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Wilson, Edwin B.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Probable Inference, the Law of Succession, and Statistical Inference</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>American Statistical Association</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1927.10502953</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>confidence-intervals-and-duality</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>§19.5 Thm 3 + Proof 2 — the score-test-inverted binomial CI known as the Wilson interval. JASA 22(158): 209-212.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CLO1934</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Clopper, Charles J. and Egon S. Pearson</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>The Use of Confidence or Fiducial Limits Illustrated in the Case of the Binomial</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1934</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Biometrika Trust</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/26.4.404</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>confidence-intervals-and-duality</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>§19.6 Thm 4 + Proof 3 — the exact beta-quantile binomial CI via beta-binomial duality. Biometrika 26(4): 404-413.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BRO2001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Brown, Lawrence D., T. Tony Cai, and Anirban DasGupta</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Interval Estimation for a Binomial Proportion</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Institute of Mathematical Statistics</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/ss/1009213286</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>confidence-intervals-and-duality</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>§19.5 Rem 10 and §19.8 Ex 12 — quantitative characterization of Wald's coverage pathology. Statistical Science 16(2): 101-133.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AGR1998</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agresti, Alan and Brent A. Coull</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Approximate Is Better than 'Exact' for Interval Estimation of Binomial Proportions</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>American Statistical Association</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/00031305.1998.10480550</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>confidence-intervals-and-duality</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>§19.5 Rem 9 — the 'plus-4' approximation to Wilson. The American Statistician 52(2): 119-126.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SCH1987</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Schuirmann, Donald J.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A Comparison of the Two One-Sided Tests Procedure and the Power Approach for Assessing the Equivalence of Average Bioavailability</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Plenum</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/BF01068419</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>confidence-intervals-and-duality</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>§19.9 Thm 7 + Exs 13-14 — the TOST procedure for equivalence testing; FDA bioequivalence 80/125 standard. J. Pharmacokinetics and Biopharmaceutics 15(6): 657-680.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NEY1937</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Neyman, Jerzy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Outline of a Theory of Statistical Estimation Based on the Classical Theory of Probability</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1937</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Royal Society</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1098/rsta.1937.0005</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>confidence-intervals-and-duality</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>§19.1 Rem 1 and §19.2 — original formulation of the CI concept as distinct from fiducial/Bayesian posterior probability. Phil. Trans. Roy. Soc. A 236(767): 333-380.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>hypothesis-testing, confidence-intervals-and-duality</t>
+          <t>hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2702,13 +2702,11 @@
       <c r="D47" t="n">
         <v>1927</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>American Statistical Association</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/01621459.1927.10502953</t>
@@ -2749,13 +2747,11 @@
       <c r="D48" t="n">
         <v>1934</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>Biometrika Trust</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/biomet/26.4.404</t>
@@ -2796,13 +2792,11 @@
       <c r="D49" t="n">
         <v>2001</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>Institute of Mathematical Statistics</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>https://doi.org/10.1214/ss/1009213286</t>
@@ -2843,13 +2837,11 @@
       <c r="D50" t="n">
         <v>1998</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>American Statistical Association</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00031305.1998.10480550</t>
@@ -2890,13 +2882,11 @@
       <c r="D51" t="n">
         <v>1987</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>Plenum</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/BF01068419</t>
@@ -2937,13 +2927,11 @@
       <c r="D52" t="n">
         <v>1937</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>Royal Society</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>https://doi.org/10.1098/rsta.1937.0005</t>
@@ -2962,6 +2950,751 @@
       <c r="K52" t="inlineStr">
         <is>
           <t>§19.1 Rem 1 and §19.2 — original formulation of the CI concept as distinct from fiducial/Bayesian posterior probability. Phil. Trans. Roy. Soc. A 236(767): 333-380.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEB2003</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>George A. F. Seber &amp; Alan J. Lee</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Linear Regression Analysis</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>978-0-471-41540-4</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/9780471722199</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>linear-regression</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Definitive Normal-linear-model reference. Ch. 3 Gauss–Markov + hat matrix; Ch. 4 F-test + simultaneous inference; Ch. 10 diagnostics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WEI2005</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sanford Weisberg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Applied Linear Regression</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>978-0-471-66379-9</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>linear-regression</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Canonical undergraduate treatment. §5.1 leverage + Cook's distance; §8.1–§8.2 residual-plot diagnostics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GRE2012</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>William H. Greene</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Econometric Analysis</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>978-0-13-139538-1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>linear-regression, generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Econometric OLS treatment. Ch. 3–4 standard coverage; §4.9 heteroscedasticity + HC-robust SEs — motivates Topic 22 sandwich estimators. Ch. 17 limited-dependent-variable models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WOR1929</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Holbrook Working &amp; Harold Hotelling</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Applications of the Theory of Error to the Interpretation of Trends</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1929</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2277011</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>linear-regression</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Originating paper for the simultaneous confidence band over regression coefficient trajectories via the F-distribution. JASA 24(165A): 73–85. §21.8 Rem 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GAL1886</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Francis Galton</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Regression Towards Mediocrity in Hereditary Stature</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1886</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2841583</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>linear-regression</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>The paper that gave "regression" its name. J. Anthropol. Inst. GB&amp;I 15: 246–263. §21.1 Rem 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GAU1823</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Carl Friedrich Gauss</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Theoria Combinationis Observationum Erroribus Minimis Obnoxiae</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1823</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Werke, IV</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>linear-regression</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Original source of both least-squares and the Gauss–Markov theorem. §21.6 joint attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MAR1900</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Andrey A. Markov</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wahrscheinlichkeitsrechnung</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Teubner</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>linear-regression</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Markov's probabilistic formalization and extension of Gauss's least-squares theorem. Completes the joint Gauss–Markov attribution. §21.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NEL1972</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>John A. Nelder &amp; Robert W. M. Wedderburn</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Generalized linear models</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1972</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2344614</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Foundational GLM paper. JRSS A 135(3): 370–384. Establishes canonical form g(μ) = x^T β, IRLS as unified fitting algorithm, deviance as goodness-of-fit. §22.1 + §22.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MCN1989</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Peter McCullagh &amp; John A. Nelder</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Generalized Linear Models</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Chapman &amp; Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>978-0-412-31760-6</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.routledge.com/Generalized-Linear-Models/McCullagh-Nelder/p/book/9780412317606</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>continuous-distributions, generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>The definitive GLM treatise. Ch. 2 canonical form, Ch. 4 binary, Ch. 6 count, Ch. 8 positive-continuous, Ch. 9 quasi-likelihood underpins §22.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AGR2015</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Alan Agresti</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Foundations of Linear and Generalized Linear Models</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>978-1-118-73003-4</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.wiley.com/en-us/Foundations+of+Linear+and+Generalized+Linear+Models-p-9781118730034</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Current standard graduate reference. Ch. 3–4 theory, Ch. 5 logistic, Ch. 7 Poisson + Gamma, Ch. 9 multinomial/ordinal (deferred). §22.4–§22.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DOB2008</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Annette J. Dobson &amp; Adrian G. Barnett</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>An Introduction to Generalized Linear Models</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Chapman &amp; Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>978-1-58488-950-2</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.routledge.com/An-Introduction-to-Generalized-Linear-Models/Dobson-Barnett/p/book/9781138741515</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Accessible introductory GLM text. Secondary reference for §22.4–§22.6 worked examples and §22.8 Wald/Score/LRT exposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WED1974</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Robert W. M. Wedderburn</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Quasi-likelihood functions, generalized linear models, and the Gauss–Newton method</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1974</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/61.3.439</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Introduces quasi-likelihood: fit by mean–variance relationship alone. Biometrika 61(3): 439–447. Basis of §22.9 QMLE + sandwich framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HUB1967</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Peter J. Huber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>The behavior of maximum likelihood estimates under nonstandard conditions</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1967</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>University of California Press</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/ebooks/berkeley-symposium-on-mathematical-statistics-and-probability/Proceedings-of-the-Fifth-Berkeley-Symposium-on-Mathematical-Statistics-and/chapter/The-behavior-of-maximum-likelihood-estimates-under-nonstandard-conditions/bsmsp/1200512988</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Asymptotic normality of MLE under model misspecification with sandwich-form variance A^-1 B A^-1. Proc. 5th Berkeley Symp. Vol 1: 221–233. §22.9 Thm 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WHI1980</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Halbert White</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A heteroskedasticity-consistent covariance matrix estimator and a direct test for heteroskedasticity</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1980</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/1912934</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Made sandwich SEs standard practice in econometrics. Econometrica 48(4): 817–838. HC0 defined here; HC1–HC3 are MacKinnon-White 1985 refinements. §22.9 sandwichSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HOS2013</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>David W. Hosmer, Stanley Lemeshow &amp; Rodney X. Sturdivant</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Applied Logistic Regression</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>978-0-470-58247-3</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/9781118548387</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Standard applied logistic-regression reference. Ch. 5 goodness-of-fit (Hosmer–Lemeshow test) is the binary-family analog of §22.9. §22.4 Rem 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FAH2013</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ludwig Fahrmeir, Thomas Kneib, Stefan Lang &amp; Brian Marx</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Regression: Models, Methods and Applications</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>978-3-642-34332-2</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-3-642-34333-9</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>generalized-linear-models</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Comprehensive regression treatment: GLMs (Ch. 5–6), GAMs (Ch. 8 — forward-pointed for Track 8), mixed-effects (Ch. 7 — forward-pointed to Track 7 / formalml.com). §22.5 + §22.6.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Citations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citations'!$A$1:$K$8</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models, regularization-and-penalized-estimation</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>point-estimation</t>
+          <t>point-estimation, regularization-and-penalized-estimation</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>large-deviations</t>
+          <t>large-deviations, regularization-and-penalized-estimation</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>point-estimation</t>
+          <t>point-estimation, regularization-and-penalized-estimation</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models</t>
+          <t>hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models, regularization-and-penalized-estimation</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3695,6 +3695,433 @@
       <c r="K68" t="inlineStr">
         <is>
           <t>Comprehensive regression treatment: GLMs (Ch. 5–6), GAMs (Ch. 8 — forward-pointed for Track 8), mixed-effects (Ch. 7 — forward-pointed to Track 7 / formalml.com). §22.5 + §22.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HOE1970</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Arthur E. Hoerl &amp; Robert W. Kennard</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Ridge regression: Biased estimation for nonorthogonal problems</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Technometrics, 12(1), 55–67</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/1267351</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Foundational ridge regression paper. Introduces (X⊤X + λI)⁻¹X⊤y, ridge trace, and the MSE-improvement theorem (Topic 23 §23.3 Thm 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>TIK1943</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Andrey N. Tikhonov</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>On the stability of inverse problems</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1943</v>
+      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Doklady Akademii Nauk SSSR, 39(5), 195–198</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://mathscinet.ams.org/mathscinet-getitem?mr=0009685</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Earliest derivation of (X⊤X + λI)⁻¹ for integral-equation regularization, 27 years before Hoerl–Kennard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>TIB1996</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Robert Tibshirani</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Regression shrinkage and selection via the lasso</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>JRSS-B, 58(1), 267–288</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2346178</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>The lasso paper. Subgradient KKT characterization and the soft-thresholding closed form for orthogonal designs (Topic 23 §23.3 Thm 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ZOU2005</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Hui Zou &amp; Trevor Hastie</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Regularization and variable selection via the elastic net</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>JRSS-B, 67(2), 301–320</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/3647580</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Elastic-net penalty α‖β‖₁ + (1-α)‖β‖₂²; strict convexity for α&lt;1; the grouping effect (Topic 23 §23.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>FRI2010</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Jerome Friedman, Trevor Hastie &amp; Robert Tibshirani</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Regularization paths for generalized linear models via coordinate descent</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Statistical Software, 33(1), 1–22</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jstatsoft.org/article/view/v033i01</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>The glmnet paper. Cyclic coordinate descent + warm-start path computation; the algorithmic backbone of Topic 23 §23.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TSE2001</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Paul Tseng</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Convergence of a block coordinate descent method for nondifferentiable minimization</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>JOTA, 109(3), 475–494</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1023/A:1017501703105</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Coordinate-descent convergence theorem for convex separable-plus-smooth objectives. Cited in Topic 23 §23.4 Thm 6 full proof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>HTW2015</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Trevor Hastie, Robert Tibshirani &amp; Martin Wainwright</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Statistical Learning with Sparsity: The Lasso and Generalizations</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Chapman &amp; Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>978-1-4987-1216-3</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>https://trevorhastie.github.io/</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive sparse-regression monograph. Ch. 4 group lasso, Ch. 6 fused / sparse-group lasso (Topic 23 §23.10 Rem 25 deferral pointer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>FAN2001</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Jianqing Fan &amp; Runze Li</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Variable selection via nonconcave penalized likelihood and its oracle properties</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>JASA, 96(456), 1348–1360</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1198/016214501753382273</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SCAD (smoothly clipped absolute deviation) non-convex penalty. Topic 23 §23.10 Rem 26 deferral pointer for non-convex regularization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>FIR1993</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>David Firth</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Bias reduction of maximum likelihood estimates</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Biometrika, 80(1), 27–38</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/80.1.27</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>generalized-linear-models, regularization-and-penalized-estimation</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Penalized likelihood via Jeffreys prior — alternative to ridge for separation in logistic regression. Cited in Topic 22 §22.4 Rem 7 and Topic 23 §23.6 Rem 11.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Citations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citations'!$A$1:$K$8</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models, regularization-and-penalized-estimation</t>
+          <t>random-variables, large-deviations, point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models, regularization-and-penalized-estimation, model-selection-and-information-criteria</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>point-estimation, regularization-and-penalized-estimation</t>
+          <t>point-estimation, regularization-and-penalized-estimation, model-selection-and-information-criteria</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>large-deviations, regularization-and-penalized-estimation</t>
+          <t>large-deviations, regularization-and-penalized-estimation, model-selection-and-information-criteria</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models, regularization-and-penalized-estimation</t>
+          <t>hypothesis-testing, confidence-intervals-and-duality, linear-regression, generalized-linear-models, regularization-and-penalized-estimation, model-selection-and-information-criteria</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4122,6 +4122,316 @@
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>Penalized likelihood via Jeffreys prior — alternative to ridge for separation in logistic regression. Cited in Topic 22 §22.4 Rem 7 and Topic 23 §23.6 Rem 11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AKA1974</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hirotugu Akaike</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>A new look at the statistical model identification</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1974</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TAC.1974.1100705</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Automatic Control, 19(6), 716–723. Introduces AIC; §24.3 Thm 1 restates with modern notation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SCH1978</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gideon Schwarz</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Estimating the dimension of a model</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1978</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aos/1176344136</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>The Annals of Statistics, 6(2), 461–464. Four-page paper introducing BIC; §24.4 Proof 2 generalizes via Laplace approximation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MAL1973</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>C. L. Mallows</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Some comments on Cp</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1973</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/00401706.1973.10489103</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Technometrics, 15(4), 661–675. Mallows' Cp for variable subset selection; §24.2 Def 3 + Ex 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STO1977</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>M. Stone</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>An asymptotic equivalence of choice of model by cross-validation and Akaike's criterion</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1977</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.2517-6161.1977.tb01603.x</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Journal of the Royal Statistical Society, Series B, 39(1), 44–47. LOO-CV ≡ AIC under Gaussian-linear errors; §24.5 Thm 4 + Proof 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>YAN2005</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Yuhong Yang</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Can the strengths of AIC and BIC be shared? A conflict between model identification and regression estimation</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2005</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/92.4.937</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Biometrika, 92(4), 937–950. Incompatibility theorem; §24.6 Thm 5 (proof outside scope, minimax lower-bound argument).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BUR2002</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kenneth P. Burnham &amp; David R. Anderson</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Model Selection and Multimodel Inference: A Practical Information-Theoretic Approach</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>978-0-387-95364-9</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/b97636</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Most widely cited applied reference on AIC; §24.3 Rem 5 AICc, §24.4 Rem 7 Akaike weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CLA2008</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Gerda Claeskens &amp; Nils Lid Hjort</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Model Selection and Model Averaging</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>978-0-521-85225-8</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/CBO9780511790485</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>model-selection-and-information-criteria</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Canonical modern textbook; Ch. 2 AIC + proofs, Ch. 3 BIC + consistency, Ch. 4 model averaging. §24.3 Rem 6 TIC; §24.4 Thm 3; §24.10 Rem 19.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Citations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citations'!$A$1:$K$8</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maximum-likelihood, method-of-moments</t>
+          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>hypothesis-testing</t>
+          <t>hypothesis-testing, bayesian-computation-and-mcmc</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4432,6 +4432,449 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>Canonical modern textbook; Ch. 2 AIC + proofs, Ch. 3 BIC + consistency, Ch. 4 model averaging. §24.3 Rem 6 TIC; §24.4 Thm 3; §24.10 Rem 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MET1953</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nicholas Metropolis, Arianna W. Rosenbluth, Marshall N. Rosenbluth, Augusta H. Teller &amp; Edward Teller</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Equation of State Calculations by Fast Computing Machines</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Journal of Chemical Physics 21(6): 1087-1092</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1063/1.1699114</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Historical origin of the Metropolis algorithm (symmetric-proposal special case of the MH featured theorem).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HAS1970</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>W. K. Hastings</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Monte Carlo sampling methods using Markov chains and their applications</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Biometrika 57(1): 97-109</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/57.1.97</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Generalization of MET1953 to asymmetric proposals; the version Topic 26 proves in MH featured theorem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GEM1984</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Stuart Geman &amp; Donald Geman</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Stochastic Relaxation, Gibbs Distributions, and the Bayesian Restoration of Images</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Pattern Analysis and Machine Intelligence 6(6): 721-741</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TPAMI.1984.4767596</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Origin of Gibbs sampling (named for Gibbs distributions of statistical mechanics).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NEA2011</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Radford M. Neal</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MCMC using Hamiltonian dynamics</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CRC Press (Handbook of MCMC, Ch. 5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.mcmchandbook.net/HandbookChapter5.pdf</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Canonical HMC reference. Cited in the HMC section for leapfrog volume preservation (section 5.2), time reversibility (section 5.3), symplectic-integrator construction (section 5.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>HOF2014</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Matthew D. Hoffman &amp; Andrew Gelman</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>The No-U-Turn Sampler: Adaptively Setting Path Lengths in Hamiltonian Monte Carlo</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Journal of Machine Learning Research 15(47): 1593-1623</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://jmlr.org/papers/v15/hoffman14a.html</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NUTS definition and correctness proof (cited stated-only in the NUTS section).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GEL1992</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Andrew Gelman &amp; Donald B. Rubin</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Inference from Iterative Simulation Using Multiple Sequences</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Statistical Science 7(4): 457-472</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/ss/1177011136</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Origin of the R-hat diagnostic. Cited in the convergence-diagnostics section. Vehtari 2021 rank-normalized split R-hat is the modern refinement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MEY2009</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sean P. Meyn &amp; Richard L. Tweedie</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Markov Chains and Stochastic Stability</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>978-0-521-73182-9</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/CBO9780511626630</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Definitive Markov-chain-theory reference. Cited for detailed-balance-implies-invariance (Thm 1.6) and for the full ergodic theorem (Thm 17.0.1), with section 5.1 Athreya-Ney splitting and section 17.1 renewal theorem for the sketch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ROB2004</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Christian P. Robert &amp; George Casella</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Monte Carlo Statistical Methods</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>978-0-387-21239-5</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-1-4757-4145-2</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Applied MCMC reference. The MH optimal-scaling example cites Ch. 7; ESS formulation cites Ch. 12; failure modes cite Ch. 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BRO2011</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Steve Brooks, Andrew Gelman, Galin L. Jones &amp; Xiao-Li Meng (Editors)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Handbook of Markov Chain Monte Carlo</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CRC Press</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>978-1-4200-7941-8</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.mcmchandbook.net/</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>bayesian-computation-and-mcmc</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Umbrella reference; contains NEA2011 as Ch. 5. Forward-map remarks cite Ch. 3 (RJMCMC Green 1995), Ch. 4 (adaptive MCMC), Ch. 11 (parallel tempering).</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Citations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citations'!$A$1:$K$8</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>hypothesis-testing, bayesian-computation-and-mcmc</t>
+          <t>hypothesis-testing, bayesian-computation-and-mcmc, bayesian-model-comparison-and-bma</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4454,13 +4454,11 @@
       <c r="D85" t="n">
         <v>1953</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Journal of Chemical Physics 21(6): 1087-1092</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>https://doi.org/10.1063/1.1699114</t>
@@ -4501,13 +4499,11 @@
       <c r="D86" t="n">
         <v>1970</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>Biometrika 57(1): 97-109</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/biomet/57.1.97</t>
@@ -4548,13 +4544,11 @@
       <c r="D87" t="n">
         <v>1984</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>IEEE Transactions on Pattern Analysis and Machine Intelligence 6(6): 721-741</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>https://doi.org/10.1109/TPAMI.1984.4767596</t>
@@ -4595,13 +4589,11 @@
       <c r="D88" t="n">
         <v>2011</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>CRC Press (Handbook of MCMC, Ch. 5)</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>https://www.mcmchandbook.net/HandbookChapter5.pdf</t>
@@ -4642,13 +4634,11 @@
       <c r="D89" t="n">
         <v>2014</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>Journal of Machine Learning Research 15(47): 1593-1623</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>https://jmlr.org/papers/v15/hoffman14a.html</t>
@@ -4689,13 +4679,11 @@
       <c r="D90" t="n">
         <v>1992</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>Statistical Science 7(4): 457-472</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>https://doi.org/10.1214/ss/1177011136</t>
@@ -4846,7 +4834,6 @@
       <c r="D93" t="n">
         <v>2011</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>CRC Press</t>
@@ -4875,6 +4862,561 @@
       <c r="K93" t="inlineStr">
         <is>
           <t>Umbrella reference; contains NEA2011 as Ch. 5. Forward-map remarks cite Ch. 3 (RJMCMC Green 1995), Ch. 4 (adaptive MCMC), Ch. 11 (parallel tempering).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>KAS1995</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Robert E. Kass &amp; Adrian E. Raftery</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bayes Factors</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1995</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Journal of the American Statistical Association 90(430): 773–795</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2291091</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Definitive applied Bayes-factors reference; §3.4 Lindley paradox; §4.1 Laplace–BIC equivalence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MEN1996</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Xiao-Li Meng &amp; Wing Hung Wong</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Simulating Ratios of Normalizing Constants via a Simple Identity: A Theoretical Exploration</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Statistica Sinica 6(4): 831–860</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www3.stat.sinica.edu.tw/statistica/oldpdf/A6n43.pdf</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Origin of bridge-sampling identity (§27.6 Thm 5 Proof 3) and MSE-optimal bridge function (Cor 5.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GEL1998</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Andrew Gelman &amp; Xiao-Li Meng</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Simulating Normalizing Constants: From Importance Sampling to Bridge Sampling to Path Sampling</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1998</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Statistical Science 13(2): 163–185</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/statistical-science/volume-13/issue-2/Simulating-normalizing-constants--from-importance-sampling-to-bridge-sampling/10.1214/ss/1028905934.full</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Thermodynamic integration / path sampling identity (§27.6 Thm 6). Unifies IS, bridge, path in one framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SKI2006</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>John Skilling</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Nested Sampling for General Bayesian Computation</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Bayesian Analysis 1(4): 833–859</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/bayesian-analysis/volume-1/issue-4/Nested-sampling-for-general-Bayesian-computation/10.1214/06-BA127.full</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Origin of nested sampling. §6 gives prior-mass shrinkage X_i = exp(−i/N_live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WAT2010</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sumio Watanabe</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Asymptotic Equivalence of Bayes Cross Validation and Widely Applicable Information Criterion in Singular Learning Theory</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Journal of Machine Learning Research 11: 3571–3594</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.jmlr.org/papers/v11/watanabe10a.html</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>WAIC definition (§27.8) + WAIC ≈ LOO asymptotic equivalence (stated-and-cited).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VEH2017</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Aki Vehtari, Andrew Gelman &amp; Jonah Gabry</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Practical Bayesian Model Evaluation Using Leave-One-Out Cross-Validation and WAIC</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Statistics and Computing 27(5): 1413–1432</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/article/10.1007/s11222-016-9696-4</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>PSIS-LOO implementation (§27.8): Pareto-smoothed importance sampling + k-hat diagnostic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>EFR2010</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Large-Scale Inference: Empirical Bayes Methods for Estimation, Testing, and Prediction</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>978-0-521-19249-1</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.cambridge.org/core/books/largescale-inference/A0B183B0080A92966497F12CE5D12589</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Two-groups model and local FDR (§27.9 Ex 11). Ch. 5 on empirical-null central-matching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SPI2002</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>David J. Spiegelhalter, Nicola G. Best, Bradley P. Carlin &amp; Angelika van der Linde</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bayesian Measures of Model Complexity and Fit</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2002</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Journal of the Royal Statistical Society: Series B 64(4): 583–639</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://rss.onlinelibrary.wiley.com/doi/10.1111/1467-9868.00353</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>DIC definition and effective-parameter-count p_DIC (§27.8 Ex 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LIN1957</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Dennis V. Lindley</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>A Statistical Paradox</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1957</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Biometrika 44(1–2): 187–192</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2333251</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Original statement of the paradox §27.5 proves. Five-page note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>JEF1961</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Harold Jeffreys</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Theory of Probability</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1961</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Oxford University Press</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>978-0-19-853193-2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://global.oup.com/academic/product/the-theory-of-probability-9780198503682</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>bayesian-foundations-and-prior-selection, bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Source of the Jeffreys scale (§27.4 Table). Reused from Topic 25 (Jeffreys priors).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HOE1999</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Jennifer A. Hoeting, David Madigan, Adrian E. Raftery &amp; Chris T. Volinsky</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Bayesian Model Averaging: A Tutorial</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Statistical Science 14(4): 382–401</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/statistical-science/volume-14/issue-4/Bayesian-model-averaging--a-tutorial-with-comments-by-M/10.1214/ss/1009212519.full</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Canonical BMA tutorial (§27.7). Occam’s-window pruning + applied case studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>GEL1996</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Andrew Gelman, Xiao-Li Meng &amp; Hal Stern</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Posterior Predictive Assessment of Model Fitness via Realized Discrepancies</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Statistica Sinica 6(4): 733–760</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www3.stat.sinica.edu.tw/statistica/oldpdf/A6n41.pdf</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Journal Article</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bayesian-model-comparison-and-bma</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Origin of Bayesian posterior-predictive p-value p_B (§27.9 Ex 12).</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics</t>
+          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>point-estimation, regularization-and-penalized-estimation</t>
+          <t>point-estimation, regularization-and-penalized-estimation, hierarchical-bayes-and-partial-pooling</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>hypothesis-testing, bayesian-computation-and-mcmc, bayesian-model-comparison-and-bma</t>
+          <t>hypothesis-testing, bayesian-computation-and-mcmc, bayesian-model-comparison-and-bma, hierarchical-bayes-and-partial-pooling</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>bayesian-computation-and-mcmc</t>
+          <t>bayesian-computation-and-mcmc, hierarchical-bayes-and-partial-pooling</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5417,6 +5417,456 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>Origin of Bayesian posterior-predictive p-value p_B (§27.9 Ex 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>JAM1961</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Willard James, Charles Stein</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Estimation with Quadratic Loss</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1961</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Proceedings of the Fourth Berkeley Symposium on Mathematical Statistics and Probability, vol. 1, pp. 361–379</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/ebooks/berkeley-symposium-on-mathematical-statistics-and-probability/Proceedings-of-the-Fourth-Berkeley-Symposium-on-Mathematical-Statistics-and/chapter/Estimation-with-Quadratic-Loss/bsmsp/1200512173</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>James–Stein estimator + closed-form risk dominance result. Used in §28.5 Thm 2 and Proof 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EFR1973</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bradley Efron, Carl Morris</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Stein's Estimation Rule and Its Competitors — an Empirical Bayes Approach</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Journal of the American Statistical Association, 68(341), pp. 117–130</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2284155</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Positive-part JS (§28.5 Rem 11) and empirical-Bayes rereading of shrinkage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LIN1972</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Dennis V. Lindley, Adrian F. M. Smith</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bayes Estimates for the Linear Model</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Journal of the Royal Statistical Society: Series B, 34(1), pp. 1–41</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2985048</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Origin of Bayesian partial pooling in hierarchical linear models (§28.6 Rem 13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LAI1982</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nan M. Laird, James H. Ware</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Random-Effects Models for Longitudinal Data</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1982</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Biometrics, 38(4), pp. 963–974</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2529876</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Canonical linear mixed-effects model (§28.8 Def 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>GEL2006</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Andrew Gelman</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Prior Distributions for Variance Parameters in Hierarchical Models</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Bayesian Analysis, 1(3), pp. 515–534</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/bayesian-analysis/volume-1/issue-3/Prior-distributions-for-variance-parameters-in-hierarchical-models-comment-on/10.1214/06-BA117A.full</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Half-Cauchy hyperpriors on τ — modern default (§28.7 Rem 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>HAR1977</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>David A. Harville</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Maximum Likelihood Approaches to Variance Component Estimation and to Related Problems</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1977</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Journal of the American Statistical Association, 72(358), pp. 320–338</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/2286796</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>REML as frequentist-mixed-models companion (§28.8 Rem 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>BRO2003</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>William J. Browne, David Draper</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>A Comparison of Bayesian and Likelihood-Based Methods for Fitting Multilevel Models</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Bayesian Analysis, 1(3), pp. 473–514</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/bayesian-analysis/volume-1/issue-3/A-comparison-of-Bayesian-and-likelihood-based-methods-for-fitting/10.1214/06-BA117.full</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Head-to-head Bayesian vs likelihood multilevel methods (§28.8 background).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>RUB1981</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Donald B. Rubin</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Estimation in Parallel Randomized Experiments</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Journal of Educational Statistics, 6(4), pp. 377–401</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.jstor.org/stable/1164617</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>8-schools dataset — spine example across §§28.1/28.4/28.6/28.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>BET2015</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Michael Betancourt, Mark Girolami</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hamiltonian Monte Carlo for Hierarchical Models</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Current Trends in Bayesian Methodology with Applications (Chapman &amp; Hall/CRC), pp. 79–101</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1312.0906</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Chapter</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>§3 develops funnel-geometry analysis cited in §28.9 Thm 7 Proof 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KLE2012</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Bas J. K. Kleijn, Aad W. van der Vaart</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>The Bernstein–Von Mises Theorem under Misspecification</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Electronic Journal of Statistics, 6, pp. 354–381</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/electronic-journal-of-statistics/volume-6/issue-none/The-Bernstein-Von-Mises-theorem-under-misspecification/10.1214/12-EJS675.full</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>hierarchical-bayes-and-partial-pooling</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>BvM under misspecification; cited in §28.7 Thm 5 as the Type-II MLE consistency source.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation</t>
+          <t>sample-spaces, conditional-probability, random-variables, large-deviations, point-estimation, order-statistics-and-quantiles</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling</t>
+          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling, order-statistics-and-quantiles</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc</t>
+          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5867,6 +5867,466 @@
       <c r="K115" t="inlineStr">
         <is>
           <t>BvM under misspecification; cited in §28.7 Thm 5 as the Type-II MLE consistency source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BAH1966</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Raghu Raj Bahadur</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>A Note on Quantiles in Large Samples</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1966</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 37(3): 577–580</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-37/issue-3/A-Note-on-Quantiles-in-Large-Samples/10.1214/aoms/1177699450.full</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Original Bahadur representation of the sample quantile; featured theorem of Topic 29 §29.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KIE1967</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jack Kiefer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>On Bahadur's Representation of Sample Quantiles</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1967</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 38(5): 1323–1342</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-38/issue-5/On-Bahadurs-Representation-of-Sample-Quantiles/10.1214/aoms/1177698690.full</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Sharpens Bahadur remainder to O_p(n^{-3/4} √log n); §29.6 Thm 6 quotes the Kiefer rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>REN1953</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Alfréd Rényi</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>On the Theory of Order Statistics</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1953</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Acta Mathematica Academiae Scientiarum Hungaricae 4(3–4): 191–231</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/BF02127580</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Origin of the exponential-spacings representation; §29.3 Thm 3 full proof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DVO1956</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Aryeh Dvoretzky, Jack Kiefer &amp; Jacob Wolfowitz</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Asymptotic Minimax Character of the Sample Distribution Function and of the Classical Multinomial Estimator</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1956</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 27(3): 642–669</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-27/issue-3/Asymptotic-Minimax-Character-of-the-Sample-Distribution-Function-and-of/10.1214/aoms/1177728174.full</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Original DKW paper (sub-optimal constant); §29.5 Thm 6 attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MAS1990</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pascal Massart</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>The Tight Constant in the Dvoretzky–Kiefer–Wolfowitz Inequality</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Annals of Probability 18(3): 1269–1283</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-probability/volume-18/issue-3/The-Tight-Constant-in-the-Dvoretzky-Kiefer-Wolfowitz-Inequality/10.1214/aop/1176990746.full</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Proves C=2 is optimal in DKW; §29.5 Thm 6 uses Massart constant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SMI1948</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nikolai Vasilyevich Smirnov</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Table for Estimating the Goodness of Fit of Empirical Distributions</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1948</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 19(2): 279–281</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-19/issue-2/Table-for-Estimating-the-Goodness-of-Fit-of-Empirical-Distributions/10.1214/aoms/1177730256.full</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Finite-sample formula for the KS null distribution; §29.8 Thm 7 attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KOL1933</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Andrey Nikolaevich Kolmogorov</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sulla determinazione empirica di una legge di distribuzione</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1933</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Giornale dell'Istituto Italiano degli Attuari 4: 83–91</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Historical Italian journal; no stable URL available. §29.8 Rem 13 attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DAV2003</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Herbert Aron David &amp; Haikady Navada Nagaraja</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Order Statistics</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>978-0-471-38926-2</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/0471722162</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Standard reference for order statistics; §29.2 Thm 1 attribution (Ch. 2); §29.2 Rem 3 cites Ch. 5–6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>HYN1996</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rob J. Hyndman &amp; Yanan Fan</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sample Quantiles in Statistical Packages</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>The American Statistician 50(4): 361–365</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/00031305.1996.10473566</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Establishes nine quantile-definition conventions; §29.4 Def 3 adopts Type 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SER1980</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Robert J. Serfling</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Approximation Theorems of Mathematical Statistics</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>978-0-471-02403-3</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/9780470316481</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>central-limit-theorem, point-estimation, order-statistics-and-quantiles</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>§2.3 on order statistics; §2.5 on quantile functions (Bahadur proof citation); §2.4 on the ECDF. Referenced by Topic 29 §29.6 Proof 2.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Citations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Citations'!$A$1:$K$8</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling, order-statistics-and-quantiles</t>
+          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling, order-statistics-and-quantiles, kernel-density-estimation</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles</t>
+          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles, kernel-density-estimation</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6321,12 +6321,442 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>central-limit-theorem, point-estimation, order-statistics-and-quantiles</t>
+          <t>central-limit-theorem, point-estimation, order-statistics-and-quantiles, kernel-density-estimation</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
           <t>§2.3 on order statistics; §2.5 on quantile functions (Bahadur proof citation); §2.4 on the ECDF. Referenced by Topic 29 §29.6 Proof 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ROS1956</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Murray Rosenblatt</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Remarks on Some Nonparametric Estimates of a Density Function</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1956</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 27(3): 832–837</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-27/issue-3/Remarks-on-Some-Nonparametric-Estimates-of-a-Density-Function/10.1214/aoms/1177728190.full</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>The founding paper of kernel smoothing. Bias-variance framework; bias is O(h²) under regularity. §30.4 Rem 7 Rosenblatt no-free-lunch attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PAR1962</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Emanuel Parzen</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>On Estimation of a Probability Density Function and Mode</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 33(3): 1065–1076</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-33/issue-3/On-Estimation-of-a-Probability-Density-Function-and-Mode/10.1214/aoms/1177704472.full</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Generalizes Rosenblatt to arbitrary symmetric kernels; proves pointwise asymptotic normality. §30.7 Thm 6 Parzen's theorem attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>EPA1969</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Vassiliy A. Epanechnikov</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Non-Parametric Estimation of a Multivariate Probability Density</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1969</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Theory of Probability &amp; Its Applications 14(1): 153–158</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://epubs.siam.org/doi/10.1137/1114019</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Proves the MISE-optimal kernel is K_E(u) = (3/4)(1 − u²) 1{|u| ≤ 1}. §30.6 Thm 5 Epanechnikov optimality short-proof attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SIL1986</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bernard W. Silverman</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Density Estimation for Statistics and Data Analysis</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Chapman and Hall</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>978-0-412-24620-3</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.taylorfrancis.com/books/mono/10.1201/9781315140919/density-estimation-statistics-data-analysis-bernard-silverman</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Standard monograph on univariate KDE. §3.4 derives ĥ_ROT = 1.06 σ̂ n^(−1/5) (and the robust min(σ̂, IQR/1.34) variant) used in §30.8 Thm 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SHJ1991</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Simon J. Sheather, M. Chris Jones</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>A Reliable Data-Based Bandwidth Selection Method for Kernel Density Estimation</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1991</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Journal of the Royal Statistical Society: Series B (Methodological) 53(3): 683–690</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.2517-6161.1991.tb01857.x</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>The plug-in bandwidth selector — gold standard. §30.8 Thm 7 name-check; §30.8 Ex 10 + PluginBandwidthComparator component benchmark against SHJ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>WAN1995</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>M. P. Wand, M. C. Jones</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Kernel Smoothing</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1995</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Chapman and Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>978-0-412-55270-0</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.taylorfrancis.com/books/mono/10.1201/b14876/kernel-smoothing-wand-jones</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Modern monograph. §2.5 has the MISE/AMISE development (§30.5–§30.6); §3 has the bandwidth-selection catalog (§30.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FAN1996</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Jianqing Fan, Irène Gijbels</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Local Polynomial Modelling and Its Applications</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Chapman and Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>978-0-412-98321-4</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://www.taylorfrancis.com/books/mono/10.1201/9780203748725/local-polynomial-modelling-applications-jianqing-fan</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Local polynomial generalization that fixes KDE's boundary bias and extends to covariate-conditional regression. §30.5 Rem 9 name-check; §30.9 Rem 17 forwards kernel regression to formalml.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DUO2007</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tarn Duong</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ks: Kernel Density Estimation and Kernel Discriminant Analysis for Multivariate Data in R</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2007</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Journal of Statistical Software 21(7): 1–16</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.18637/jss.v021.i07</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>The ks R package reference — de-facto multivariate KDE implementation. §30.10 Rem 21 standard multivariate tool citation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SCO2015</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>David W. Scott</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Multivariate Density Estimation: Theory, Practice, and Visualization</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>978-0-471-69755-8</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/9781118575574</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>kernel-density-estimation</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Multivariate-KDE reference. §30.6 Rem 13 cites Ch. 6 for the multivariate AMISE rate O(n^{-4/(4+d)}) — the curse of dimensionality. §30.10 Rem 21 forward-pointer.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling, order-statistics-and-quantiles, kernel-density-estimation</t>
+          <t>point-estimation, maximum-likelihood, method-of-moments, sufficient-statistics, hierarchical-bayes-and-partial-pooling, order-statistics-and-quantiles, kernel-density-estimation, bootstrap</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles, kernel-density-estimation</t>
+          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles, kernel-density-estimation, bootstrap</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>hierarchical-bayes-and-partial-pooling</t>
+          <t>hierarchical-bayes-and-partial-pooling, bootstrap</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>central-limit-theorem, point-estimation, order-statistics-and-quantiles, kernel-density-estimation</t>
+          <t>central-limit-theorem, point-estimation, order-statistics-and-quantiles, kernel-density-estimation, bootstrap</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -6757,6 +6757,421 @@
       <c r="K134" t="inlineStr">
         <is>
           <t>Multivariate-KDE reference. §30.6 Rem 13 cites Ch. 6 for the multivariate AMISE rate O(n^{-4/(4+d)}) — the curse of dimensionality. §30.10 Rem 21 forward-pointer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BIF1981</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Peter J. Bickel &amp; David A. Freedman</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Some Asymptotic Theory for the Bootstrap</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>The Annals of Statistics 9(6): 1196–1217</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-9/issue-6/Some-Asymptotic-Theory-for-the-Bootstrap/10.1214/aos/1176345637.full</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Bootstrap consistency theorem; foundational for §31.3 Theorem 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>EFR1979</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bootstrap Methods: Another Look at the Jackknife</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1979</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>The Annals of Statistics 7(1): 1–26</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-7/issue-1/Bootstrap-Methods-Another-Look-at-the-Jackknife/10.1214/aos/1176344552.full</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Founding paper of the bootstrap; introduces resampling from F_n as a plug-in alternative to the jackknife.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>EFR1987</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Better Bootstrap Confidence Intervals</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Journal of the American Statistical Association 82(397): 171–185</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1987.10478410</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Introduces BCa (bias-corrected accelerated) CI; §31.4 Def 5 and §31.5 Thm 5 cite this paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>EFT1993</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bradley Efron &amp; Robert J. Tibshirani</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>An Introduction to the Bootstrap</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1993</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Chapman &amp; Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>978-0-412-04231-7</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.routledge.com/An-Introduction-to-the-Bootstrap/Efron-Tibshirani/p/book/9780412042317</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Book-length bootstrap treatment; Ch. 14 on BCa, Ch. 17 on bootstrap tests, Ch. 10 on smoothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HAL1992</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Peter Hall</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>The Bootstrap and Edgeworth Expansion</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>978-1-4612-4384-7</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-1-4612-4384-7</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Edgeworth-expansion analysis of bootstrap accuracy; §31.5 Theorem 5 is Hall Thm 3.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>KUN1989</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Hans R. Künsch</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>The Jackknife and the Bootstrap for General Stationary Observations</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1989</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>The Annals of Statistics 17(3): 1217–1241</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-17/issue-3/The-Jackknife-and-the-Bootstrap-for-General-Stationary-Observations/10.1214/aos/1176347265.full</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Block bootstrap for dependent data; §31.10 Rem 17 cites as the dependent-observations generalization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>POR1994</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Dimitris N. Politis &amp; Joseph P. Romano</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Large Sample Confidence Regions Based on Subsamples under Minimal Assumptions</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>The Annals of Statistics 22(4): 2031–2050</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-22/issue-4/Large-Sample-Confidence-Regions-Based-on-Subsamples-Under-Minimal-Assumptions/10.1214/aos/1176325770.full</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Subsampling as without-replacement alternative; §31.10 Rem 18 pointer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SIN1981</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Kesar Singh</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>On the Asymptotic Accuracy of Efron's Bootstrap</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>The Annals of Statistics 9(6): 1187–1195</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-9/issue-6/On-the-Asymptotic-Accuracy-of-Efrons-Bootstrap/10.1214/aos/1176345636.full</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Companion asymptotic-accuracy paper to Bickel-Freedman 1981; Edgeworth-expansion-based percentile-CI accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SIY1987</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Bernard W. Silverman &amp; G. Alastair Young</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>The Bootstrap: To Smooth or Not to Smooth?</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Biometrika 74(3): 469–479</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/74.3.469</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>bootstrap</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Smooth-bootstrap foundational paper; §31.8 Definition 9 matches this construction.</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles, kernel-density-estimation, bootstrap</t>
+          <t>maximum-likelihood, method-of-moments, bayesian-computation-and-mcmc, order-statistics-and-quantiles, kernel-density-estimation, bootstrap, empirical-processes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -7172,6 +7172,721 @@
       <c r="K143" t="inlineStr">
         <is>
           <t>Smooth-bootstrap foundational paper; §31.8 Definition 9 matches this construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>VDW1996</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Aad W. van der Vaart, Jon A. Wellner</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Weak Convergence and Empirical Processes: With Applications to Statistics</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>978-0-387-94640-5</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-1-4757-2545-2</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Standard reference; source for Topic 32 §32.3 notation, §32.5 Donsker-proof structure, §32.6 bracketing-integral bound, §32.7 Hadamard-differentiability framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>KOS2008</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Michael R. Kosorok</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Introduction to Empirical Processes and Semiparametric Inference</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>978-0-387-74977-8</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-0-387-74978-5</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Modern readable treatment; Ch. 9 functional-delta exposition templates Topic 32 §32.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>POL1984</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>David Pollard</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Convergence of Stochastic Processes</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>978-0-387-90990-6</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-1-4612-5254-2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Covering-number route to uniform convergence; Ch. II symmetrisation is §32.4 proof template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>POL1990</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>David Pollard</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Empirical Processes: Theory and Applications</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>NSF-CBMS Regional Conference Series</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>978-0-940-60016-4</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/ebooks/nsf-cbms-regional-conference-series-in-probability-and-statistics/Empirical-Processes--Theory-and-Applications/toc/10.1214/cbms/1462061091</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Short monograph; §32.6 metric-entropy exposition follows §4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DUD1978</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>R. M. Dudley</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Central Limit Theorems for Empirical Measures</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Annals of Probability 6(6): 899-929</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-probability/volume-6/issue-6/Central-Limit-Theorems-for-Empirical-Measures/10.1214/aop/1176995384.full</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Founding paper for Donsker classes + bracketing-integral condition. §32.6 Thm 4 is Dudley’s theorem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DUD1999</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>R. M. Dudley</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Uniform Central Limit Theorems</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>978-0-521-46102-3</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.cambridge.org/core/books/uniform-central-limit-theorems/AE550D3CDFD1F2A23D4089CCA92C7518</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Ch. 3-4 metric-entropy integral + Brownian-bridge-construction proofs are §32.5 technical sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>GIN2016</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Evarist Giné, Richard Nickl</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mathematical Foundations of Infinite-Dimensional Statistical Models</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>978-1-107-04316-9</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.cambridge.org/core/books/mathematical-foundations-of-infinitedimensional-statistical-models/C9D2A07B20A0F37F89EF78998E44A1B1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Modern nonparametric-statistics treatise; §32.6 bracketing bounds and §32.10 Rem 23 Banach-space-CLT pointer follow Ch. 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TAL1996</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Michel Talagrand</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>New Concentration Inequalities in Product Spaces</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Inventiones Mathematicae 126(3): 505-563</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/article/10.1007/s002220050108</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Supersedes Bernstein/Bennett for empirical processes; §32.9 Thm 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>LED1991</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Michel Ledoux, Michel Talagrand</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Probability in Banach Spaces: Isoperimetry and Processes</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1991</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Springer Ergebnisse der Mathematik</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>978-3-540-52013-9</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/book/10.1007/978-3-642-20212-4</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Concentration, Gaussian processes, entropy methods in the Banach-space setting; §32.9 + §32.10 Rem 23 cite repeatedly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VAP1971</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>V. N. Vapnik, A. Ya. Chervonenkis</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>On the Uniform Convergence of Relative Frequencies of Events to Their Probabilities</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1971</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Theory of Probability and Its Applications 16(2): 264-280</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1137/1116025</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Founding paper of VC theory; §32.4 Thm 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SAU1972</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Norbert Sauer</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>On the Density of Families of Sets</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1972</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Journal of Combinatorial Theory, Series A 13(1): 145-147</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/0097-3165(72)90019-2</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Sauer’s lemma; §32.4 Thm 1 (stated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>DON1952</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Monroe D. Donsker</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Justification and Extension of Doob’s Heuristic Approach to the Kolmogorov-Smirnov Theorems</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1952</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 23(2): 277-281</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-mathematical-statistics/volume-23/issue-2/Justification-and-Extension-of-Doobs-Heuristic-Approach-to-the-Kolmogorov/10.1214/aoms/1177729445.full</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>empirical-processes</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Founding paper of the classical functional CLT; §32.5 featured theorem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BIL1999</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Patrick Billingsley</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Convergence of Probability Measures</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>978-0-471-19745-4</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/book/10.1002/9780470316962</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>modes-of-convergence, central-limit-theorem, order-statistics-and-quantiles, bootstrap, empirical-processes</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Classical weak-convergence-in-metric-spaces reference; §14 (Brownian bridge) and §16 (Donsker in D[0,1]) cited throughout Topic 32.</t>
         </is>
       </c>
     </row>
